--- a/artfynd/A 48816-2025 artfynd.xlsx
+++ b/artfynd/A 48816-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132821131</v>
+        <v>132821190</v>
       </c>
       <c r="B2" t="n">
-        <v>58119</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571652</v>
+        <v>571625</v>
       </c>
       <c r="R2" t="n">
-        <v>7203572</v>
+        <v>7203468</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132821190</v>
+        <v>132821131</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>58136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,27 +798,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571625</v>
+        <v>571652</v>
       </c>
       <c r="R3" t="n">
-        <v>7203468</v>
+        <v>7203572</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
